--- a/product_order_forms/015_vista_coffeeteria_order_form_final--product_order_forms.xlsx
+++ b/product_order_forms/015_vista_coffeeteria_order_form_final--product_order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>date_of_birth</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Date of Birth</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>order_time</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Order Time</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>order_note</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Order Note</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>price</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>Price</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,200 +773,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>quantity</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Integer</t>
+          <t>Quantity</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>option_3</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Option 3</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>option_4</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Option 4</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>option_5</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Option 5</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Time</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Decimal</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Integer</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>option_6</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Option 6</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -983,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1016,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Apple</t>
         </is>
       </c>
     </row>
@@ -1033,12 +849,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>banana</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Banana</t>
         </is>
       </c>
     </row>
@@ -1050,12 +866,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Orange</t>
         </is>
       </c>
     </row>
@@ -1067,12 +883,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Apple</t>
         </is>
       </c>
     </row>
@@ -1084,12 +900,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>banana</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Banana</t>
         </is>
       </c>
     </row>
@@ -1101,216 +917,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>option_3_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>option_3_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>option_3_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>option_4_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>option_4_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>option_4_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>option_5_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>option_5_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>option_5_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>option_6_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>option_6_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>option_6_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>Orange</t>
         </is>
       </c>
     </row>
